--- a/bu_WEATHER_FEED_CATALOG.xlsx
+++ b/bu_WEATHER_FEED_CATALOG.xlsx
@@ -1,29 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/587ce551b77ccc82/Documents/PlatformIO/Projects/ESP32-Weather-Aggragator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{989E3563-8B0F-4FEE-90E3-6FC740B2CBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50A94056-0BB6-4109-A73C-D5C393CE19ED}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{989E3563-8B0F-4FEE-90E3-6FC740B2CBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{448D9BAB-3B37-4AF8-ADC1-A39D7ABC6087}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-2910" windowWidth="29040" windowHeight="15720" xr2:uid="{962BD6D7-0243-4F9A-A79E-196D6F841A54}"/>
+    <workbookView xWindow="43080" yWindow="-2910" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{962BD6D7-0243-4F9A-A79E-196D6F841A54}"/>
   </bookViews>
   <sheets>
-    <sheet name="WEATHER_FEED_CATALOG" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="WEATHER_FEED_CATALOG" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WEATHER_FEED_CATALOG!$A$1:$J$412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WEATHER_FEED_CATALOG!$A$1:$J$412</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <pivotCaches>
+    <pivotCache cacheId="3" r:id="rId3"/>
+  </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3639" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3650" uniqueCount="921">
   <si>
     <t>project</t>
   </si>
@@ -2777,6 +2781,15 @@
   </si>
   <si>
     <t>OM_Past</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Count of outgoing_aio_feed</t>
   </si>
 </sst>
 </file>
@@ -3281,11 +3294,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3346,6 +3364,5074 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Dana Kamp" refreshedDate="46323.272623726851" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="411" xr:uid="{BCF9C75B-116E-4C58-8B50-D05F287331A0}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:J412" sheet="WEATHER_FEED_CATALOG"/>
+  </cacheSource>
+  <cacheFields count="10">
+    <cacheField name="project" numFmtId="0">
+      <sharedItems count="8">
+        <s v="NWS Alerts"/>
+        <s v="Apple_Weatherkit"/>
+        <s v="Feed-Avg"/>
+        <s v="NWS Forecasts"/>
+        <s v="OM"/>
+        <s v="Open_Meteo"/>
+        <s v="Open_Weather"/>
+        <s v="WAPI"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="feed_source" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="script" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="incoming_source" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="incoming_field" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="outgoing_aio_feed" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="value_or_transform" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="desired_update_minutes" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1440"/>
+    </cacheField>
+    <cacheField name="estimated_interval" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="notes" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="411">
+  <r>
+    <x v="0"/>
+    <s v="NWS_Alerts"/>
+    <s v="code.py"/>
+    <s v="NWS /alerts/active?point={LATITUDE},{LONGITUDE}"/>
+    <s v="short alert fields + description"/>
+    <s v="big-alert"/>
+    <s v="rotating full alert text"/>
+    <n v="1"/>
+    <s v="publish check every 15 s; only changed values sent"/>
+    <s v="No alerts: three text feeds receive No Current Alerts once per change; failed fetch retains previous alerts."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.asOf"/>
+    <s v="currentasof"/>
+    <s v="raw"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.cloudCover"/>
+    <s v="currentcloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.cloudCoverHighAltPct"/>
+    <s v="currentcloudcoverhighaltpct"/>
+    <s v="int(x*100), percent"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.cloudCoverLowAltPct"/>
+    <s v="currentcloudcoverlowaltpct"/>
+    <s v="int(x*100), percent"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.cloudCoverMidAltPct"/>
+    <s v="currentcloudcovermidaltpct"/>
+    <s v="int(x*100), percent"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.conditionCode"/>
+    <s v="currentconditioncode"/>
+    <s v="raw"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.daylight"/>
+    <s v="currentdaylight"/>
+    <s v="light/dark text; current uses Its light/Its dark; hourly uses It will be light/dark"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.humidity"/>
+    <s v="currenthumidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.precipitationIntensity"/>
+    <s v="currentprecipitationintensity"/>
+    <s v="raw"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.pressure"/>
+    <s v="currentpressure"/>
+    <s v="raw"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.pressureTrend"/>
+    <s v="currentpressuretrend"/>
+    <s v="raw"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.temperature"/>
+    <s v="currenttemperature"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.temperatureApparent"/>
+    <s v="currenttemperatureapparent"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.temperatureDewPoint"/>
+    <s v="currenttemperaturedewpoint"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.uvIndex"/>
+    <s v="currentuv"/>
+    <s v="raw"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.visibility"/>
+    <s v="currentvisibility"/>
+    <s v="int(x*0.00062137), whole miles"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.windDirection"/>
+    <s v="currentwinddegrees"/>
+    <s v="raw"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.windDirection"/>
+    <s v="currentwinddirection"/>
+    <s v="16-point compass text"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.windGust"/>
+    <s v="currentwindgust"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="current.windSpeed"/>
+    <s v="currentwindspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.conditionCode"/>
+    <s v="days1conditioncode"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.cloudCover"/>
+    <s v="days1daytimecloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.conditionCode"/>
+    <s v="days1daytimeconditioncode"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.forecastEnd"/>
+    <s v="days1daytimeend"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.humidity"/>
+    <s v="days1daytimehumidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.precipitationAmount"/>
+    <s v="days1daytimeprecipitationamount"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.precipitationChance"/>
+    <s v="days1daytimeprecipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.precipitationType"/>
+    <s v="days1daytimeprecipitationtype"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.snowfallAmount"/>
+    <s v="days1daytimesnowfallamount"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.forecastStart"/>
+    <s v="days1daytimestart"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.temperatureMax"/>
+    <s v="days1daytimetemperaturemax"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.temperatureMin"/>
+    <s v="days1daytimetemperaturemin"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.windDirection"/>
+    <s v="days1daytimewinddirection"/>
+    <s v="16-point compass text"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.windGustSpeedMax"/>
+    <s v="days1daytimewindgustspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.windSpeed"/>
+    <s v="days1daytimewindspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.daytimeForecast.windSpeedMax"/>
+    <s v="days1daytimewindspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.forecastEnd"/>
+    <s v="days1end"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.maxUvIndex"/>
+    <s v="days1maxuvindex"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.moonPhase"/>
+    <s v="days1moonphase"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.moonrise"/>
+    <s v="days1moonrise"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.moonset"/>
+    <s v="days1moonset"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.cloudCover"/>
+    <s v="days1ovntcloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.conditionCode"/>
+    <s v="days1ovntconditioncode"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.forecastEnd"/>
+    <s v="days1ovntend"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.humidity"/>
+    <s v="days1ovnthumidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.precipitationAmount"/>
+    <s v="days1ovntprecipitationamount"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.precipitationChance"/>
+    <s v="days1ovntprecipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.precipitationType"/>
+    <s v="days1ovntprecipitationtype"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.snowfallAmount"/>
+    <s v="days1ovntsnowfallamount"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.forecastStart"/>
+    <s v="days1ovntstart"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.temperatureMax"/>
+    <s v="days1ovnttemperaturemax"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.temperatureMin"/>
+    <s v="days1ovnttemperaturemin"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.windDirection"/>
+    <s v="days1ovntwinddirection"/>
+    <s v="16-point compass text"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.windGustSpeedMax"/>
+    <s v="days1ovntwindgustspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.windSpeed"/>
+    <s v="days1ovntwindspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.overnightForecast.windSpeedMax"/>
+    <s v="days1ovntwindspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.precipitationAmount"/>
+    <s v="days1precipitationamount"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.precipitationChance"/>
+    <s v="days1precipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.precipitationType"/>
+    <s v="days1precipitationtype"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.snowfallAmount"/>
+    <s v="days1snowfallamount"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.solarMidnight"/>
+    <s v="days1solarmidnight"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.solarNoon"/>
+    <s v="days1solarnoon"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.forecastStart"/>
+    <s v="days1start"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.sunrise"/>
+    <s v="days1sunrise"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.sunriseAstronomical"/>
+    <s v="days1sunriseastronomical"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.sunriseCivil"/>
+    <s v="days1sunrisecivil"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.sunriseNautical"/>
+    <s v="days1sunrisenautical"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.sunset"/>
+    <s v="days1sunset"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.sunsetAstronomical"/>
+    <s v="days1sunsetastronomical"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.sunsetCivil"/>
+    <s v="days1sunsetcivil"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.sunsetNautical"/>
+    <s v="days1sunsetnautical"/>
+    <s v="raw"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.temperatureMax"/>
+    <s v="days1temperaturemax"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.temperatureMin"/>
+    <s v="days1temperaturemin"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.windGustSpeedMax"/>
+    <s v="days1windgustspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.windSpeedAvg"/>
+    <s v="days1windspeedavg"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_1.windSpeedMax"/>
+    <s v="days1windspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="120"/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.conditionCode"/>
+    <s v="days2conditioncode"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.cloudCover"/>
+    <s v="days2daytimecloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.conditionCode"/>
+    <s v="days2daytimeconditioncode"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.forecastEnd"/>
+    <s v="days2daytimeend"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.humidity"/>
+    <s v="days2daytimehumidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.precipitationAmount"/>
+    <s v="days2daytimeprecipitationamount"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.precipitationChance"/>
+    <s v="days2daytimeprecipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.precipitationType"/>
+    <s v="days2daytimeprecipitationtype"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.snowfallAmount"/>
+    <s v="days2daytimesnowfallamount"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.forecastStart"/>
+    <s v="days2daytimestart"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.temperatureMax"/>
+    <s v="days2daytimetemperaturemax"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.temperatureMin"/>
+    <s v="days2daytimetemperaturemin"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.windDirection"/>
+    <s v="days2daytimewinddirection"/>
+    <s v="16-point compass text"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.windGustSpeedMax"/>
+    <s v="days2daytimewindgustspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.windSpeed"/>
+    <s v="days2daytimewindspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.daytimeForecast.windSpeedMax"/>
+    <s v="days2daytimewindspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.forecastEnd"/>
+    <s v="days2end"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.maxUvIndex"/>
+    <s v="days2maxuvindex"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.moonPhase"/>
+    <s v="days2moonphase"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.moonrise"/>
+    <s v="days2moonrise"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.moonset"/>
+    <s v="days2moonset"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.cloudCover"/>
+    <s v="days2ovntcloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.conditionCode"/>
+    <s v="days2ovntconditioncode"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.forecastEnd"/>
+    <s v="days2ovntend"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.humidity"/>
+    <s v="days2ovnthumidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.precipitationAmount"/>
+    <s v="days2ovntprecipitationamount"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.precipitationChance"/>
+    <s v="days2ovntprecipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.precipitationType"/>
+    <s v="days2ovntprecipitationtype"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.snowfallAmount"/>
+    <s v="days2ovntsnowfallamount"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.forecastStart"/>
+    <s v="days2ovntstart"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.temperatureMax"/>
+    <s v="days2ovnttemperaturemax"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.temperatureMin"/>
+    <s v="days2ovnttemperaturemin"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.windDirection"/>
+    <s v="days2ovntwinddirection"/>
+    <s v="16-point compass text"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.windGustSpeedMax"/>
+    <s v="days2ovntwindgustspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.windSpeed"/>
+    <s v="days2ovntwindspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.overnightForecast.windSpeedMax"/>
+    <s v="days2ovntwindspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.precipitationAmount"/>
+    <s v="days2precipitationamount"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.precipitationChance"/>
+    <s v="days2precipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.precipitationType"/>
+    <s v="days2precipitationtype"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.snowfallAmount"/>
+    <s v="days2snowfallamount"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.solarMidnight"/>
+    <s v="days2solarmidnight"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.solarNoon"/>
+    <s v="days2solarnoon"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.forecastStart"/>
+    <s v="days2start"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.sunrise"/>
+    <s v="days2sunrise"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.sunriseAstronomical"/>
+    <s v="days2sunriseastronomical"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.sunriseCivil"/>
+    <s v="days2sunrisecivil"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.sunriseNautical"/>
+    <s v="days2sunrisenautical"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.sunset"/>
+    <s v="days2sunset"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.sunsetAstronomical"/>
+    <s v="days2sunsetastronomical"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.sunsetCivil"/>
+    <s v="days2sunsetcivil"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.sunsetNautical"/>
+    <s v="days2sunsetnautical"/>
+    <s v="raw"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.temperatureMax"/>
+    <s v="days2temperaturemax"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.temperatureMin"/>
+    <s v="days2temperaturemin"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.windGustSpeedMax"/>
+    <s v="days2windgustspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.windSpeedAvg"/>
+    <s v="days2windspeedavg"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_2.windSpeedMax"/>
+    <s v="days2windspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="240"/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.conditionCode"/>
+    <s v="days5conditioncode"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.cloudCover"/>
+    <s v="days5daytimecloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.conditionCode"/>
+    <s v="days5daytimeconditioncode"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.forecastEnd"/>
+    <s v="days5daytimeend"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.humidity"/>
+    <s v="days5daytimehumidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.precipitationAmount"/>
+    <s v="days5daytimeprecipitationamount"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.precipitationChance"/>
+    <s v="days5daytimeprecipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.precipitationType"/>
+    <s v="days5daytimeprecipitationtype"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.snowfallAmount"/>
+    <s v="days5daytimesnowfallamount"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.forecastStart"/>
+    <s v="days5daytimestart"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.temperatureMax"/>
+    <s v="days5daytimetemperaturemax"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.temperatureMin"/>
+    <s v="days5daytimetemperaturemin"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.windDirection"/>
+    <s v="days5daytimewinddirection"/>
+    <s v="16-point compass text"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.windGustSpeedMax"/>
+    <s v="days5daytimewindgustspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.windSpeed"/>
+    <s v="days5daytimewindspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.daytimeForecast.windSpeedMax"/>
+    <s v="days5daytimewindspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.forecastEnd"/>
+    <s v="days5end"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.maxUvIndex"/>
+    <s v="days5maxuvindex"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.moonPhase"/>
+    <s v="days5moonphase"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.moonrise"/>
+    <s v="days5moonrise"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.moonset"/>
+    <s v="days5moonset"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.cloudCover"/>
+    <s v="days5ovntcloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.conditionCode"/>
+    <s v="days5ovntconditioncode"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.forecastEnd"/>
+    <s v="days5ovntend"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.humidity"/>
+    <s v="days5ovnthumidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.precipitationAmount"/>
+    <s v="days5ovntprecipitationamount"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.precipitationChance"/>
+    <s v="days5ovntprecipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.precipitationType"/>
+    <s v="days5ovntprecipitationtype"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.snowfallAmount"/>
+    <s v="days5ovntsnowfallamount"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.forecastStart"/>
+    <s v="days5ovntstart"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.temperatureMax"/>
+    <s v="days5ovnttemperaturemax"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.temperatureMin"/>
+    <s v="days5ovnttemperaturemin"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.windDirection"/>
+    <s v="days5ovntwinddirection"/>
+    <s v="16-point compass text"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.windGustSpeedMax"/>
+    <s v="days5ovntwindgustspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.windSpeed"/>
+    <s v="days5ovntwindspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.overnightForecast.windSpeedMax"/>
+    <s v="days5ovntwindspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.precipitationAmount"/>
+    <s v="days5precipitationamount"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.precipitationChance"/>
+    <s v="days5precipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.precipitationType"/>
+    <s v="days5precipitationtype"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.snowfallAmount"/>
+    <s v="days5snowfallamount"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.solarMidnight"/>
+    <s v="days5solarmidnight"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.solarNoon"/>
+    <s v="days5solarnoon"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.forecastStart"/>
+    <s v="days5start"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.sunrise"/>
+    <s v="days5sunrise"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.sunriseAstronomical"/>
+    <s v="days5sunriseastronomical"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.sunriseCivil"/>
+    <s v="days5sunrisecivil"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.sunriseNautical"/>
+    <s v="days5sunrisenautical"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.sunset"/>
+    <s v="days5sunset"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.sunsetAstronomical"/>
+    <s v="days5sunsetastronomical"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.sunsetCivil"/>
+    <s v="days5sunsetcivil"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.sunsetNautical"/>
+    <s v="days5sunsetnautical"/>
+    <s v="raw"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.temperatureMax"/>
+    <s v="days5temperaturemax"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.temperatureMin"/>
+    <s v="days5temperaturemin"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.windGustSpeedMax"/>
+    <s v="days5windgustspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.windSpeedAvg"/>
+    <s v="days5windspeedavg"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_days_5.windSpeedMax"/>
+    <s v="days5windspeedmax"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="720"/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Temp_Avgr"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO latest feed data"/>
+    <s v="om-temp: value + created_at"/>
+    <s v="feed-avg"/>
+    <s v="arithmetic mean of eligible F values; metadata ele=eligible count"/>
+    <n v="2"/>
+    <s v="~5-10 min + network; ~10 min when all four valid"/>
+    <s v="Eligibility: calculated age &lt;30 min; fixed +5 h correction; skip output if no valid inputs; gtemp disabled."/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Temp_Avgr"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO latest feed data"/>
+    <s v="openweather.owtemp: value + created_at"/>
+    <s v="feed-avg"/>
+    <s v="arithmetic mean of eligible F values; metadata ele=eligible count"/>
+    <n v="2"/>
+    <s v="~5-10 min + network; ~10 min when all four valid"/>
+    <s v="Eligibility: calculated age &lt;30 min; fixed +5 h correction; skip output if no valid inputs; gtemp disabled."/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Temp_Avgr"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO latest feed data"/>
+    <s v="wapi.temperature: value + created_at"/>
+    <s v="feed-avg"/>
+    <s v="arithmetic mean of eligible F values; metadata ele=eligible count"/>
+    <n v="2"/>
+    <s v="~5-10 min + network; ~10 min when all four valid"/>
+    <s v="Eligibility: calculated age &lt;30 min; fixed +5 h correction; skip output if no valid inputs; gtemp disabled."/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Temp_Avgr"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO latest feed data"/>
+    <s v="currenttemperature: value + created_at"/>
+    <s v="feed-avg"/>
+    <s v="arithmetic mean of eligible F values; metadata ele=eligible count"/>
+    <n v="5"/>
+    <s v="~5-10 min + network; ~10 min when all four valid"/>
+    <s v="Eligibility: calculated age &lt;30 min; fixed +5 h correction; skip output if no valid inputs; gtemp disabled."/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="NWS_Alerts"/>
+    <s v="code.py"/>
+    <s v="NWS /alerts/active?point={LATITUDE},{LONGITUDE}"/>
+    <s v="features[:5].properties.parameters.NWSheadline + headline"/>
+    <s v="headline-alert"/>
+    <s v="rotating headline text"/>
+    <n v="1"/>
+    <s v="publish check every 15 s; only changed values sent"/>
+    <s v="No alerts: three text feeds receive No Current Alerts once per change; failed fetch retains previous alerts."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.cloudCover"/>
+    <s v="hours12cloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.conditionCode"/>
+    <s v="hours12conditioncode"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.daylight"/>
+    <s v="hours12daylight"/>
+    <s v="light/dark text; current uses Its light/Its dark; hourly uses It will be light/dark"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.humidity"/>
+    <s v="hours12humidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.precipitationAmount"/>
+    <s v="hours12precipitationamount"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.precipitationChance"/>
+    <s v="hours12precipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.precipitationIntensity"/>
+    <s v="hours12precipitationintensity"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.precipitationType"/>
+    <s v="hours12precipitationtype"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.pressure"/>
+    <s v="hours12pressure"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.pressureTrend"/>
+    <s v="hours12pressuretrend"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.snowfallAmount"/>
+    <s v="hours12snowfallamount"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.snowfallIntensity"/>
+    <s v="hours12snowfallintensity"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.forecastStart"/>
+    <s v="hours12start"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.temperature"/>
+    <s v="hours12temperature"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.temperatureApparent"/>
+    <s v="hours12temperatureapparent"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.temperatureDewPoint"/>
+    <s v="hours12temperaturedewpoint"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.uvIndex"/>
+    <s v="hours12uvindex"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.visibility"/>
+    <s v="hours12visibility"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.windDirection"/>
+    <s v="hours12winddirection"/>
+    <s v="16-point compass text"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.windGust"/>
+    <s v="hours12windgust"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_12.windSpeed"/>
+    <s v="hours12windspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="10"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.cloudCover"/>
+    <s v="hours1cloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.conditionCode"/>
+    <s v="hours1conditioncode"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.daylight"/>
+    <s v="hours1daylight"/>
+    <s v="light/dark text; current uses Its light/Its dark; hourly uses It will be light/dark"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.humidity"/>
+    <s v="hours1humidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.precipitationAmount"/>
+    <s v="hours1precipitationamount"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.precipitationChance"/>
+    <s v="hours1precipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.precipitationIntensity"/>
+    <s v="hours1precipitationintensity"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.precipitationType"/>
+    <s v="hours1precipitationtype"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.pressure"/>
+    <s v="hours1pressure"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.pressureTrend"/>
+    <s v="hours1pressuretrend"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.snowfallAmount"/>
+    <s v="hours1snowfallamount"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.snowfallIntensity"/>
+    <s v="hours1snowfallintensity"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.forecastStart"/>
+    <s v="hours1start"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.temperature"/>
+    <s v="hours1temperature"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.temperatureApparent"/>
+    <s v="hours1temperatureapparent"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.temperatureDewPoint"/>
+    <s v="hours1temperaturedewpoint"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.uvIndex"/>
+    <s v="hours1uvindex"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.visibility"/>
+    <s v="hours1visibility"/>
+    <s v="raw"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.windDirection"/>
+    <s v="hours1winddirection"/>
+    <s v="16-point compass text"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.windGust"/>
+    <s v="hours1windgust"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_1.windSpeed"/>
+    <s v="hours1windspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="10"/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.cloudCover"/>
+    <s v="hours24cloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.conditionCode"/>
+    <s v="hours24conditioncode"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.daylight"/>
+    <s v="hours24daylight"/>
+    <s v="light/dark text; current uses Its light/Its dark; hourly uses It will be light/dark"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.humidity"/>
+    <s v="hours24humidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.precipitationAmount"/>
+    <s v="hours24precipitationamount"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.precipitationChance"/>
+    <s v="hours24precipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.precipitationIntensity"/>
+    <s v="hours24precipitationintensity"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.precipitationType"/>
+    <s v="hours24precipitationtype"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.pressure"/>
+    <s v="hours24pressure"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.pressureTrend"/>
+    <s v="hours24pressuretrend"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.snowfallAmount"/>
+    <s v="hours24snowfallamount"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.snowfallIntensity"/>
+    <s v="hours24snowfallintensity"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.forecastStart"/>
+    <s v="hours24start"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.temperature"/>
+    <s v="hours24temperature"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.temperatureApparent"/>
+    <s v="hours24temperatureapparent"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.temperatureDewPoint"/>
+    <s v="hours24temperaturedewpoint"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.uvIndex"/>
+    <s v="hours24uvindex"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.visibility"/>
+    <s v="hours24visibility"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.windDirection"/>
+    <s v="hours24winddirection"/>
+    <s v="16-point compass text"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.windGust"/>
+    <s v="hours24windgust"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_24.windSpeed"/>
+    <s v="hours24windspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.cloudCover"/>
+    <s v="hours2cloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.conditionCode"/>
+    <s v="hours2conditioncode"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.daylight"/>
+    <s v="hours2daylight"/>
+    <s v="light/dark text; current uses Its light/Its dark; hourly uses It will be light/dark"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.humidity"/>
+    <s v="hours2humidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.precipitationAmount"/>
+    <s v="hours2precipitationamount"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.precipitationChance"/>
+    <s v="hours2precipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.precipitationIntensity"/>
+    <s v="hours2precipitationintensity"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.precipitationType"/>
+    <s v="hours2precipitationtype"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.pressure"/>
+    <s v="hours2pressure"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.pressureTrend"/>
+    <s v="hours2pressuretrend"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.snowfallAmount"/>
+    <s v="hours2snowfallamount"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.snowfallIntensity"/>
+    <s v="hours2snowfallintensity"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.forecastStart"/>
+    <s v="hours2start"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.temperature"/>
+    <s v="hours2temperature"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.temperatureApparent"/>
+    <s v="hours2temperatureapparent"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.temperatureDewPoint"/>
+    <s v="hours2temperaturedewpoint"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.uvIndex"/>
+    <s v="hours2uvindex"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.visibility"/>
+    <s v="hours2visibility"/>
+    <s v="raw"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.windDirection"/>
+    <s v="hours2winddirection"/>
+    <s v="16-point compass text"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.windGust"/>
+    <s v="hours2windgust"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_2.windSpeed"/>
+    <s v="hours2windspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="30"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.cloudCover"/>
+    <s v="hours6cloudcover"/>
+    <s v="int(x*100), percent"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.conditionCode"/>
+    <s v="hours6conditioncode"/>
+    <s v="raw"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.daylight"/>
+    <s v="hours6daylight"/>
+    <s v="light/dark text; current uses Its light/Its dark; hourly uses It will be light/dark"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.humidity"/>
+    <s v="hours6humidity"/>
+    <s v="int(x*100), percent"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.precipitationAmount"/>
+    <s v="hours6precipitationamount"/>
+    <s v="raw"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.precipitationChance"/>
+    <s v="hours6precipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.precipitationIntensity"/>
+    <s v="hours6precipitationintensity"/>
+    <s v="raw"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.precipitationType"/>
+    <s v="hours6precipitationtype"/>
+    <s v="raw"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.pressure"/>
+    <s v="hours6pressure"/>
+    <s v="raw"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.pressureTrend"/>
+    <s v="hours6pressuretrend"/>
+    <s v="raw"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.snowfallAmount"/>
+    <s v="hours6snowfallamount"/>
+    <s v="raw"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.snowfallIntensity"/>
+    <s v="hours6snowfallintensity"/>
+    <s v="raw"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.forecastStart"/>
+    <s v="hours6start"/>
+    <s v="raw"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.temperature"/>
+    <s v="hours6temperature"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.temperatureApparent"/>
+    <s v="hours6temperatureapparent"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.temperatureDewPoint"/>
+    <s v="hours6temperaturedewpoint"/>
+    <s v="C to F, rounded to 1 decimal"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.uvIndex"/>
+    <s v="hours6uvindex"/>
+    <s v="raw"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.visibility"/>
+    <s v="hours6visibility"/>
+    <s v="raw"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.windDirection"/>
+    <s v="hours6winddirection"/>
+    <s v="16-point compass text"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.windGust"/>
+    <s v="hours6windgust"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_hours_6.windSpeed"/>
+    <s v="hours6windspeed"/>
+    <s v="int(x*0.62137119), mph as implemented"/>
+    <n v="60"/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_minutes_30.precipitationChance"/>
+    <s v="m30precipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_minutes_30.precipitationIntensity"/>
+    <s v="m30precipitationintensity"/>
+    <s v="raw"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_minutes_30.startTime"/>
+    <s v="m30starttime"/>
+    <s v="raw"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_minutes_5.precipitationChance"/>
+    <s v="m5precipitationchance"/>
+    <s v="int(x*100), percent"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_minutes_5.precipitationIntensity"/>
+    <s v="m5precipitationintensity"/>
+    <s v="raw"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO weather integration; location 2738; Apple WeatherKit"/>
+    <s v="forecast_minutes_5.startTime"/>
+    <s v="m5starttime"/>
+    <s v="raw"/>
+    <n v="5"/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="Sleep-only steady-state mean; network, reload and throttle time additional; missing labels publish string 0."/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="NWS_Alerts"/>
+    <s v="code.py"/>
+    <s v="NWS /alerts/active?point={LATITUDE},{LONGITUDE}"/>
+    <s v="len(features[:5])"/>
+    <s v="nbr-alerts"/>
+    <s v="count capped at 5"/>
+    <n v="1"/>
+    <s v="~5 min fetch; count sent only when changed"/>
+    <s v="No alerts: three text feeds receive No Current Alerts once per change; failed fetch retains previous alerts."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[0]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.00"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="60"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[1]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.01"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="60"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[2]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.02"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[3]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.03"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[4]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.04"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[5]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.05"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[6]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.06"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[7]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.07"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[8]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.08"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[9]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.09"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[10]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.10"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[11]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.11"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[12]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.12"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="NWS /gridpoints/MEG/54,68/forecast"/>
+    <s v="properties.periods[13]: name, startTime, endTime, isDaytime, temperature, windSpeed, windDirection, detailedForecast"/>
+    <s v="nws.13"/>
+    <s v="formatted period forecast; temperature labeled F"/>
+    <n v="720"/>
+    <s v="&gt;=60 min 14 s + 14 NWS GETs + AIO traffic"/>
+    <s v="Separate full NWS request for each period; shortForecast and number also read but not included in output."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="Adafruit IO nws.13 latest data"/>
+    <s v="data[0].created_at"/>
+    <s v="nws.when"/>
+    <s v="timestamp shifted by fixed -6 hours"/>
+    <n v="60"/>
+    <s v="once per hourly batch if nws.13 history nonempty"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="OM_Current"/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.cloud_cover"/>
+    <s v="om-clouds"/>
+    <s v="percent"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="OM_Current"/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.*"/>
+    <s v="om-current"/>
+    <s v="formatted current summary; includes is_day and weather_code description"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="OM_Current"/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.weather_code"/>
+    <s v="om-desc"/>
+    <s v="description lookup"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="OM_Current"/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.apparent_temperature"/>
+    <s v="om-fl"/>
+    <s v="F"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="OM_Current"/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.relative_humidity_2m"/>
+    <s v="om-hum"/>
+    <s v="percent"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="OM_Current"/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.* (not daily history)"/>
+    <s v="om-past"/>
+    <s v="current summary copied to historical-named feed"/>
+    <n v="60"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="om-past contains current summary, not the daily summaries."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="OM_Past"/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily[*] for 1 day(s) ago"/>
+    <s v="ompast.0"/>
+    <s v="formatted historical daily summary"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="Index 0 is yesterday; dynamic feed key; summary has no dated metadata."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily[*] for 2 day(s) ago"/>
+    <s v="ompast.1"/>
+    <s v="formatted historical daily summary"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="Index 0 is yesterday; dynamic feed key; summary has no dated metadata."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily[*] for 3 day(s) ago"/>
+    <s v="ompast.2"/>
+    <s v="formatted historical daily summary"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="Index 0 is yesterday; dynamic feed key; summary has no dated metadata."/>
+  </r>
+  <r>
+    <x v="5"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily[*] for 4 day(s) ago"/>
+    <s v="ompast.3"/>
+    <s v="formatted historical daily summary"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 13 min + overhead"/>
+    <s v="Index 0 is yesterday; dynamic feed key; summary has no dated metadata."/>
+  </r>
+  <r>
+    <x v="5"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily[*] for 5 day(s) ago"/>
+    <s v="ompast.4"/>
+    <s v="formatted historical daily summary"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 13 min + overhead"/>
+    <s v="Index 0 is yesterday; dynamic feed key; summary has no dated metadata."/>
+  </r>
+  <r>
+    <x v="5"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily[*] for 6 day(s) ago"/>
+    <s v="ompast.5"/>
+    <s v="formatted historical daily summary"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 13 min + overhead"/>
+    <s v="Index 0 is yesterday; dynamic feed key; summary has no dated metadata."/>
+  </r>
+  <r>
+    <x v="5"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily[*] for 7 day(s) ago"/>
+    <s v="ompast.6"/>
+    <s v="formatted historical daily summary"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 13 min + overhead"/>
+    <s v="Index 0 is yesterday; dynamic feed key; summary has no dated metadata."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily.daylight_duration[i]"/>
+    <s v="omp-daylighthours"/>
+    <s v="int(seconds/3600*10)/10 hours"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="3 writes per feed per refresh, oldest to newest; dated metadata; refresh on counter 0."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily.temperature_2m_max[i]"/>
+    <s v="omp-maxtemp"/>
+    <s v="F"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="3 writes per feed per refresh, oldest to newest; dated metadata; refresh on counter 0."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily.temperature_2m_min[i]"/>
+    <s v="omp-mintemp"/>
+    <s v="F"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="3 writes per feed per refresh, oldest to newest; dated metadata; refresh on counter 0."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily.rain_sum[i]"/>
+    <s v="omp-rain"/>
+    <s v="API-selected inches"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="3 writes per feed per refresh, oldest to newest; dated metadata; refresh on counter 0."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.pressure_msl"/>
+    <s v="om-pres"/>
+    <s v="raw pressure; current_units.pressure_msl"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.pressure_msl + AIO om-pres latest 5 values"/>
+    <s v="om-pres-trend"/>
+    <s v="Rising/Falling/Steady; Unknown when history unavailable"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily.showers_sum[i]"/>
+    <s v="omp-showers"/>
+    <s v="API-selected inches"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="3 writes per feed per refresh, oldest to newest; dated metadata; refresh on counter 0."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily.snowfall_sum[i]"/>
+    <s v="omp-snow"/>
+    <s v="raw; API snowfall units"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="3 writes per feed per refresh, oldest to newest; dated metadata; refresh on counter 0."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily.sunshine_duration[i]"/>
+    <s v="omp-sunshinehrs"/>
+    <s v="int(seconds/3600*10)/10 hours"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="3 writes per feed per refresh, oldest to newest; dated metadata; refresh on counter 0."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="daily.precipitation_sum[i]"/>
+    <s v="omp-totprec"/>
+    <s v="API-selected inches"/>
+    <n v="720"/>
+    <s v="every 24 cycles; &gt;=6 h 14 min + overhead"/>
+    <s v="3 writes per feed per refresh, oldest to newest; dated metadata; refresh on counter 0."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.rain"/>
+    <s v="om-rain"/>
+    <s v="API-selected inches"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.showers"/>
+    <s v="om-showers"/>
+    <s v="API-selected inches"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.snowfall"/>
+    <s v="om-snow"/>
+    <s v="raw; use current_units.snowfall, do not assume inches"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.temperature_2m"/>
+    <s v="om-temp"/>
+    <s v="F"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.precipitation"/>
+    <s v="om-totprec"/>
+    <s v="API-selected inches"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.time"/>
+    <s v="om-when"/>
+    <s v="API local time string"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.wind_gusts_10m"/>
+    <s v="om-windgust"/>
+    <s v="mph"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.wind_speed_10m + wind_direction_10m + wind_gusts_10m"/>
+    <s v="om-winds"/>
+    <s v="formatted wind text; compass direction"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Open-Meteo /v1/forecast; configured coordinates/timezone"/>
+    <s v="current.wind_speed_10m"/>
+    <s v="om-windspeed"/>
+    <s v="mph"/>
+    <n v="5"/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="Shares feed keys with the other Open-Meteo project; pressure history read each cycle."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="dt + timezone"/>
+    <s v="openweather.owasof"/>
+    <s v="YYYY-MM-DD HH:MM local time"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="name + sys.country"/>
+    <s v="openweather.owcity"/>
+    <s v="city, country"/>
+    <n v="1440"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="clouds.all"/>
+    <s v="openweather.owclouds"/>
+    <s v="percent"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="weather[0].description"/>
+    <s v="openweather.owdescription"/>
+    <s v="raw text"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="main.feels_like"/>
+    <s v="openweather.owfeelslike"/>
+    <s v="C to F"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="main.humidity"/>
+    <s v="openweather.owhumidity"/>
+    <s v="percent"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="weather[0].icon"/>
+    <s v="openweather.owicon"/>
+    <s v="icon identifier"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="weather[0].main"/>
+    <s v="openweather.owmaintext"/>
+    <s v="raw text"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="main.temp_max"/>
+    <s v="openweather.owmaxtemp"/>
+    <s v="C to F; unavailable defaults to 0 C"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="main.temp_min"/>
+    <s v="openweather.owmintemp"/>
+    <s v="C to F; unavailable defaults to 0 C"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="main.pressure + AIO openweather.owpressure latest 6"/>
+    <s v="openweather.owpresstrend"/>
+    <s v="Rising/Falling/Steady"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="main.pressure"/>
+    <s v="openweather.owpressure"/>
+    <s v="hPa"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="main.pressure + AIO openweather.owpressure latest 6"/>
+    <s v="openweather.owptval"/>
+    <s v="trend: Rising=1; Falling=-1; Steady=0"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="rain.1h"/>
+    <s v="openweather.owrain"/>
+    <s v="raw mm; unavailable defaults to 0"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="sys.sunrise + timezone"/>
+    <s v="openweather.owsunrise"/>
+    <s v="local HH:MM"/>
+    <n v="720"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="sys.sunset + timezone"/>
+    <s v="openweather.owsunset"/>
+    <s v="local HH:MM"/>
+    <n v="720"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="main.temp"/>
+    <s v="openweather.owtemp"/>
+    <s v="C to F"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="timezone"/>
+    <s v="openweather.owtimezone"/>
+    <s v="seconds / 3600; hours"/>
+    <n v="1440"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="visibility"/>
+    <s v="openweather.owvisibility"/>
+    <s v="meters to whole miles, truncated"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="weather[0].id"/>
+    <s v="openweather.owweatherid"/>
+    <s v="numeric code"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="wind.deg"/>
+    <s v="openweather.owwinddirection"/>
+    <s v="16-direction text using windir2 thresholds"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="wind.gust"/>
+    <s v="openweather.owwindgust"/>
+    <s v="m/s to whole mph; unavailable defaults to 0"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="wind.speed"/>
+    <s v="openweather.owwindspeed"/>
+    <s v="m/s to whole mph, truncated"/>
+    <n v="5"/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="code.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=8.19 min; rotation-dependent"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f1.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=55.85 min"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f2.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f3.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f4.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f5.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=51.19 min"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f6a.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=122.87 min"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f7a.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=61.43 min"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Apple_WK"/>
+    <s v="f8a.py"/>
+    <s v="Local script status"/>
+    <s v="last/next script; missing labels"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="mean &gt;=38.40 min"/>
+    <s v="code.py sends two normal statuses; each handler sends one; missing-label logs add writes."/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="NWS_Alerts"/>
+    <s v="code.py"/>
+    <s v="NWS /alerts/active?point={LATITUDE},{LONGITUDE}"/>
+    <s v="alert count + local fetch time"/>
+    <s v="rt"/>
+    <s v="fetch status text"/>
+    <m/>
+    <s v="~5 min on successful fetch; deduplicated"/>
+    <s v="No alerts: three text feeds receive No Current Alerts once per change; failed fetch retains previous alerts."/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="NWS_Forecasts"/>
+    <s v="code.py"/>
+    <s v="Local batch status"/>
+    <s v="forecast batch complete"/>
+    <s v="rt"/>
+    <s v="Forecasts Updated"/>
+    <m/>
+    <s v="once per hourly batch if nws.13 history nonempty"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Local script status"/>
+    <s v="current/past update completed"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="&gt;=15 min 35 s + startup/network"/>
+    <s v="One extra status on historical-refresh cycles."/>
+  </r>
+  <r>
+    <x v="5"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="Local script status"/>
+    <s v="current/past update completed"/>
+    <s v="rt"/>
+    <s v="status text"/>
+    <m/>
+    <s v="&gt;=15 min 33 s + startup/network"/>
+    <s v="One extra status on historical-refresh cycles."/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="OpenWeather /data/2.5/weather; metric query"/>
+    <s v="local update status"/>
+    <s v="rt"/>
+    <s v="OpenWeather"/>
+    <m/>
+    <s v="&gt;=30 min 12 s + network/reload"/>
+    <s v="29.5 min idle + 40 s batch pauses + 2 s after fetch; 6 pressure samples read before new write."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.last_updated"/>
+    <s v="rt"/>
+    <s v="WeatherAPI: timestamp"/>
+    <m/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.air_quality.us-epa-index"/>
+    <s v="wapi.aqi"/>
+    <s v="EPA index"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.last_updated"/>
+    <s v="wapi.as-of"/>
+    <s v="raw local time string"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.cloud"/>
+    <s v="wapi.clouds"/>
+    <s v="percent"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.condition.code"/>
+    <s v="wapi.cond-code"/>
+    <s v="numeric code; no metadata"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.condition.code"/>
+    <s v="wapi.desc"/>
+    <s v="local description lookup, not condition.text"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.dewpoint_f"/>
+    <s v="wapi.dew-point"/>
+    <s v="F"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.feelslike_f"/>
+    <s v="wapi.feels-like"/>
+    <s v="F"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.heatindex_f"/>
+    <s v="wapi.heat-index"/>
+    <s v="F"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.humidity"/>
+    <s v="wapi.humidity"/>
+    <s v="percent"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.precip_in"/>
+    <s v="wapi.precip"/>
+    <s v="inches"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.pressure_mb"/>
+    <s v="wapi.pressure"/>
+    <s v="mb"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.temp_f"/>
+    <s v="wapi.temperature"/>
+    <s v="F"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.windchill_f"/>
+    <s v="wapi.wind-chill"/>
+    <s v="F"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.wind_degree"/>
+    <s v="wapi.wind-dir"/>
+    <s v="16-point compass text"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.gust_mph"/>
+    <s v="wapi.wind-gust"/>
+    <s v="mph"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <s v="code.py"/>
+    <s v="WeatherAPI /v1/current.json; aqi=yes"/>
+    <s v="current.wind_mph"/>
+    <s v="wapi.wind-speed"/>
+    <s v="mph"/>
+    <n v="5"/>
+    <s v="&gt;=21 min 24 s + network"/>
+    <s v="30 display rounds * 7 items * 6 s; six 4-second pauses; reload after 12 fetches."/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="NWS_Alerts"/>
+    <s v="code.py"/>
+    <s v="NWS /alerts/active?point={LATITUDE},{LONGITUDE}"/>
+    <s v="features[:5].properties: senderName, sent, severity, urgency, event, headline, parameters.NWSheadline"/>
+    <s v="weather-alerts"/>
+    <s v="rotating short alert text"/>
+    <n v="1"/>
+    <s v="publish check every 15 s; only changed values sent"/>
+    <s v="No alerts: three text feeds receive No Current Alerts once per change; failed fetch retains previous alerts."/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974D433A-5FD9-4F57-83FD-8ABC67A317BB}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of outgoing_aio_feed" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3664,6 +8750,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA17A63-2B9D-4F86-A784-4618DA73E7C1}">
+  <dimension ref="A3:B12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="15.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.46484375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="B3" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="6">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B7" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="B12" s="6">
+        <v>411</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D61CBEE-D806-4C92-B6D4-2299793F4DB5}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J412"/>
@@ -3672,7 +8852,7 @@
     <col min="1" max="1" width="20.3984375" customWidth="1"/>
     <col min="2" max="2" width="16.9296875" customWidth="1"/>
     <col min="3" max="3" width="9.06640625" customWidth="1"/>
-    <col min="4" max="4" width="14.9296875" customWidth="1"/>
+    <col min="4" max="4" width="48" customWidth="1"/>
     <col min="5" max="5" width="41.73046875" customWidth="1"/>
     <col min="6" max="6" width="29.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="45.06640625" customWidth="1"/>
@@ -14956,7 +20136,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A355" s="2" t="s">
         <v>152</v>
       </c>
@@ -14986,7 +20166,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A356" s="2" t="s">
         <v>152</v>
       </c>
@@ -15016,7 +20196,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A357" s="2" t="s">
         <v>152</v>
       </c>
@@ -15046,7 +20226,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A358" s="2" t="s">
         <v>152</v>
       </c>
@@ -15076,7 +20256,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A359" s="2" t="s">
         <v>152</v>
       </c>
@@ -15106,7 +20286,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A360" s="2" t="s">
         <v>152</v>
       </c>
@@ -15136,7 +20316,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A361" s="2" t="s">
         <v>152</v>
       </c>
@@ -15166,7 +20346,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A362" s="2" t="s">
         <v>152</v>
       </c>
@@ -15196,7 +20376,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A363" s="2" t="s">
         <v>152</v>
       </c>
@@ -15226,7 +20406,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A364" s="2" t="s">
         <v>152</v>
       </c>
@@ -15256,7 +20436,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A365" s="2" t="s">
         <v>152</v>
       </c>
@@ -15286,7 +20466,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A366" s="2" t="s">
         <v>152</v>
       </c>
@@ -15316,7 +20496,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A367" s="2" t="s">
         <v>152</v>
       </c>
@@ -15346,7 +20526,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A368" s="2" t="s">
         <v>152</v>
       </c>
@@ -15376,7 +20556,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A369" s="2" t="s">
         <v>152</v>
       </c>
@@ -15406,7 +20586,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A370" s="2" t="s">
         <v>152</v>
       </c>
@@ -15436,7 +20616,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A371" s="2" t="s">
         <v>152</v>
       </c>
@@ -15466,7 +20646,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A372" s="2" t="s">
         <v>152</v>
       </c>
@@ -15496,7 +20676,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A373" s="2" t="s">
         <v>152</v>
       </c>
@@ -15526,7 +20706,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A374" s="2" t="s">
         <v>152</v>
       </c>
@@ -15556,7 +20736,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A375" s="2" t="s">
         <v>152</v>
       </c>
@@ -15586,7 +20766,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A376" s="2" t="s">
         <v>152</v>
       </c>
@@ -15616,7 +20796,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A377" s="2" t="s">
         <v>152</v>
       </c>
@@ -16120,7 +21300,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A394" s="2" t="s">
         <v>152</v>
       </c>
@@ -16148,7 +21328,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A395" s="2" t="s">
         <v>207</v>
       </c>
@@ -16176,7 +21356,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A396" s="2" t="s">
         <v>207</v>
       </c>
@@ -16206,7 +21386,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A397" s="2" t="s">
         <v>207</v>
       </c>
@@ -16236,7 +21416,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A398" s="2" t="s">
         <v>207</v>
       </c>
@@ -16266,7 +21446,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A399" s="2" t="s">
         <v>207</v>
       </c>
@@ -16296,7 +21476,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A400" s="2" t="s">
         <v>207</v>
       </c>
@@ -16326,7 +21506,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A401" s="2" t="s">
         <v>207</v>
       </c>
@@ -16356,7 +21536,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A402" s="2" t="s">
         <v>207</v>
       </c>
@@ -16386,7 +21566,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A403" s="2" t="s">
         <v>207</v>
       </c>
@@ -16416,7 +21596,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A404" s="2" t="s">
         <v>207</v>
       </c>
@@ -16446,7 +21626,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A405" s="2" t="s">
         <v>207</v>
       </c>
@@ -16476,7 +21656,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A406" s="2" t="s">
         <v>207</v>
       </c>
@@ -16506,7 +21686,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A407" s="2" t="s">
         <v>207</v>
       </c>
@@ -16536,7 +21716,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A408" s="2" t="s">
         <v>207</v>
       </c>
@@ -16566,7 +21746,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A409" s="2" t="s">
         <v>207</v>
       </c>
@@ -16596,7 +21776,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A410" s="2" t="s">
         <v>207</v>
       </c>
@@ -16626,7 +21806,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A411" s="2" t="s">
         <v>207</v>
       </c>
@@ -16692,7 +21872,7 @@
   <autoFilter ref="A1:J412" xr:uid="{9D61CBEE-D806-4C92-B6D4-2299793F4DB5}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Open_Weather"/>
+        <filter val="WAPI"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/bu_WEATHER_FEED_CATALOG.xlsx
+++ b/bu_WEATHER_FEED_CATALOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/587ce551b77ccc82/Documents/PlatformIO/Projects/ESP32-Weather-Aggragator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{989E3563-8B0F-4FEE-90E3-6FC740B2CBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{448D9BAB-3B37-4AF8-ADC1-A39D7ABC6087}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{989E3563-8B0F-4FEE-90E3-6FC740B2CBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{910A851D-54D7-4C98-9559-47EFB2705F88}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-2910" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{962BD6D7-0243-4F9A-A79E-196D6F841A54}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -3294,7 +3294,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -3303,7 +3303,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -8358,7 +8357,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974D433A-5FD9-4F57-83FD-8ABC67A317BB}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974D433A-5FD9-4F57-83FD-8ABC67A317BB}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" showAll="0">
@@ -8770,7 +8769,7 @@
       <c r="A4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>311</v>
       </c>
     </row>
@@ -8778,7 +8777,7 @@
       <c r="A5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>4</v>
       </c>
     </row>
@@ -8786,7 +8785,7 @@
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <v>5</v>
       </c>
     </row>
@@ -8794,7 +8793,7 @@
       <c r="A7" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>16</v>
       </c>
     </row>
@@ -8802,7 +8801,7 @@
       <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <v>29</v>
       </c>
     </row>
@@ -8810,7 +8809,7 @@
       <c r="A9" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9">
         <v>5</v>
       </c>
     </row>
@@ -8818,7 +8817,7 @@
       <c r="A10" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10">
         <v>24</v>
       </c>
     </row>
@@ -8826,7 +8825,7 @@
       <c r="A11" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11">
         <v>17</v>
       </c>
     </row>
@@ -8834,7 +8833,7 @@
       <c r="A12" s="5" t="s">
         <v>919</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12">
         <v>411</v>
       </c>
     </row>
@@ -20136,7 +20135,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A355" s="2" t="s">
         <v>152</v>
       </c>
@@ -20166,7 +20165,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A356" s="2" t="s">
         <v>152</v>
       </c>
@@ -20196,7 +20195,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A357" s="2" t="s">
         <v>152</v>
       </c>
@@ -20226,7 +20225,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A358" s="2" t="s">
         <v>152</v>
       </c>
@@ -20256,7 +20255,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A359" s="2" t="s">
         <v>152</v>
       </c>
@@ -20286,7 +20285,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A360" s="2" t="s">
         <v>152</v>
       </c>
@@ -20316,7 +20315,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A361" s="2" t="s">
         <v>152</v>
       </c>
@@ -20346,7 +20345,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="362" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A362" s="2" t="s">
         <v>152</v>
       </c>
@@ -20376,7 +20375,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A363" s="2" t="s">
         <v>152</v>
       </c>
@@ -20406,7 +20405,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A364" s="2" t="s">
         <v>152</v>
       </c>
@@ -20436,7 +20435,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A365" s="2" t="s">
         <v>152</v>
       </c>
@@ -20466,7 +20465,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A366" s="2" t="s">
         <v>152</v>
       </c>
@@ -20496,7 +20495,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A367" s="2" t="s">
         <v>152</v>
       </c>
@@ -20526,7 +20525,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A368" s="2" t="s">
         <v>152</v>
       </c>
@@ -20556,7 +20555,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A369" s="2" t="s">
         <v>152</v>
       </c>
@@ -20586,7 +20585,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A370" s="2" t="s">
         <v>152</v>
       </c>
@@ -20616,7 +20615,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A371" s="2" t="s">
         <v>152</v>
       </c>
@@ -20646,7 +20645,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A372" s="2" t="s">
         <v>152</v>
       </c>
@@ -20676,7 +20675,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A373" s="2" t="s">
         <v>152</v>
       </c>
@@ -20706,7 +20705,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A374" s="2" t="s">
         <v>152</v>
       </c>
@@ -20736,7 +20735,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A375" s="2" t="s">
         <v>152</v>
       </c>
@@ -20766,7 +20765,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A376" s="2" t="s">
         <v>152</v>
       </c>
@@ -20796,7 +20795,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A377" s="2" t="s">
         <v>152</v>
       </c>
@@ -21300,7 +21299,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A394" s="2" t="s">
         <v>152</v>
       </c>
@@ -21328,7 +21327,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A395" s="2" t="s">
         <v>207</v>
       </c>
@@ -21356,7 +21355,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A396" s="2" t="s">
         <v>207</v>
       </c>
@@ -21386,7 +21385,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A397" s="2" t="s">
         <v>207</v>
       </c>
@@ -21416,7 +21415,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A398" s="2" t="s">
         <v>207</v>
       </c>
@@ -21446,7 +21445,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A399" s="2" t="s">
         <v>207</v>
       </c>
@@ -21476,7 +21475,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A400" s="2" t="s">
         <v>207</v>
       </c>
@@ -21506,7 +21505,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A401" s="2" t="s">
         <v>207</v>
       </c>
@@ -21536,7 +21535,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A402" s="2" t="s">
         <v>207</v>
       </c>
@@ -21566,7 +21565,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A403" s="2" t="s">
         <v>207</v>
       </c>
@@ -21596,7 +21595,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A404" s="2" t="s">
         <v>207</v>
       </c>
@@ -21626,7 +21625,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A405" s="2" t="s">
         <v>207</v>
       </c>
@@ -21656,7 +21655,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A406" s="2" t="s">
         <v>207</v>
       </c>
@@ -21686,7 +21685,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A407" s="2" t="s">
         <v>207</v>
       </c>
@@ -21716,7 +21715,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A408" s="2" t="s">
         <v>207</v>
       </c>
@@ -21746,7 +21745,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A409" s="2" t="s">
         <v>207</v>
       </c>
@@ -21776,7 +21775,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A410" s="2" t="s">
         <v>207</v>
       </c>
@@ -21806,7 +21805,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A411" s="2" t="s">
         <v>207</v>
       </c>
@@ -21872,7 +21871,7 @@
   <autoFilter ref="A1:J412" xr:uid="{9D61CBEE-D806-4C92-B6D4-2299793F4DB5}">
     <filterColumn colId="0">
       <filters>
-        <filter val="WAPI"/>
+        <filter val="Open_Weather"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/bu_WEATHER_FEED_CATALOG.xlsx
+++ b/bu_WEATHER_FEED_CATALOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/587ce551b77ccc82/Documents/PlatformIO/Projects/ESP32-Weather-Aggragator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{989E3563-8B0F-4FEE-90E3-6FC740B2CBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{910A851D-54D7-4C98-9559-47EFB2705F88}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{989E3563-8B0F-4FEE-90E3-6FC740B2CBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09804EAA-E5A9-4744-BB05-CAF4BD198EB1}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-2910" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{962BD6D7-0243-4F9A-A79E-196D6F841A54}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -8357,7 +8357,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974D433A-5FD9-4F57-83FD-8ABC67A317BB}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{974D433A-5FD9-4F57-83FD-8ABC67A317BB}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" showAll="0">
@@ -20135,7 +20135,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A355" s="2" t="s">
         <v>152</v>
       </c>
@@ -20165,7 +20165,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A356" s="2" t="s">
         <v>152</v>
       </c>
@@ -20195,7 +20195,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A357" s="2" t="s">
         <v>152</v>
       </c>
@@ -20225,7 +20225,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A358" s="2" t="s">
         <v>152</v>
       </c>
@@ -20255,7 +20255,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A359" s="2" t="s">
         <v>152</v>
       </c>
@@ -20285,7 +20285,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A360" s="2" t="s">
         <v>152</v>
       </c>
@@ -20315,7 +20315,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A361" s="2" t="s">
         <v>152</v>
       </c>
@@ -20345,7 +20345,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A362" s="2" t="s">
         <v>152</v>
       </c>
@@ -20375,7 +20375,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A363" s="2" t="s">
         <v>152</v>
       </c>
@@ -20405,7 +20405,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A364" s="2" t="s">
         <v>152</v>
       </c>
@@ -20435,7 +20435,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A365" s="2" t="s">
         <v>152</v>
       </c>
@@ -20465,7 +20465,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A366" s="2" t="s">
         <v>152</v>
       </c>
@@ -20495,7 +20495,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A367" s="2" t="s">
         <v>152</v>
       </c>
@@ -20525,7 +20525,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A368" s="2" t="s">
         <v>152</v>
       </c>
@@ -20555,7 +20555,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A369" s="2" t="s">
         <v>152</v>
       </c>
@@ -20585,7 +20585,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A370" s="2" t="s">
         <v>152</v>
       </c>
@@ -20615,7 +20615,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A371" s="2" t="s">
         <v>152</v>
       </c>
@@ -20645,7 +20645,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A372" s="2" t="s">
         <v>152</v>
       </c>
@@ -20675,7 +20675,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A373" s="2" t="s">
         <v>152</v>
       </c>
@@ -20705,7 +20705,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A374" s="2" t="s">
         <v>152</v>
       </c>
@@ -20735,7 +20735,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A375" s="2" t="s">
         <v>152</v>
       </c>
@@ -20765,7 +20765,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A376" s="2" t="s">
         <v>152</v>
       </c>
@@ -20795,7 +20795,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A377" s="2" t="s">
         <v>152</v>
       </c>
@@ -21299,7 +21299,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A394" s="2" t="s">
         <v>152</v>
       </c>
@@ -21327,7 +21327,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A395" s="2" t="s">
         <v>207</v>
       </c>
@@ -21355,7 +21355,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A396" s="2" t="s">
         <v>207</v>
       </c>
@@ -21385,7 +21385,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A397" s="2" t="s">
         <v>207</v>
       </c>
@@ -21415,7 +21415,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A398" s="2" t="s">
         <v>207</v>
       </c>
@@ -21445,7 +21445,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A399" s="2" t="s">
         <v>207</v>
       </c>
@@ -21475,7 +21475,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A400" s="2" t="s">
         <v>207</v>
       </c>
@@ -21505,7 +21505,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A401" s="2" t="s">
         <v>207</v>
       </c>
@@ -21535,7 +21535,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A402" s="2" t="s">
         <v>207</v>
       </c>
@@ -21565,7 +21565,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A403" s="2" t="s">
         <v>207</v>
       </c>
@@ -21595,7 +21595,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A404" s="2" t="s">
         <v>207</v>
       </c>
@@ -21625,7 +21625,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A405" s="2" t="s">
         <v>207</v>
       </c>
@@ -21655,7 +21655,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A406" s="2" t="s">
         <v>207</v>
       </c>
@@ -21685,7 +21685,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A407" s="2" t="s">
         <v>207</v>
       </c>
@@ -21715,7 +21715,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A408" s="2" t="s">
         <v>207</v>
       </c>
@@ -21745,7 +21745,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A409" s="2" t="s">
         <v>207</v>
       </c>
@@ -21775,7 +21775,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A410" s="2" t="s">
         <v>207</v>
       </c>
@@ -21805,7 +21805,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A411" s="2" t="s">
         <v>207</v>
       </c>
@@ -21871,7 +21871,7 @@
   <autoFilter ref="A1:J412" xr:uid="{9D61CBEE-D806-4C92-B6D4-2299793F4DB5}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Open_Weather"/>
+        <filter val="WAPI"/>
       </filters>
     </filterColumn>
   </autoFilter>
